--- a/deliverables/附录1：测试用例清单_已填写.xlsx
+++ b/deliverables/附录1：测试用例清单_已填写.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Googledownload\test2-main\test2-main\deliverables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Googledownload\test2-main\test2\deliverables\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Information文档信息" sheetId="1" r:id="rId1"/>
@@ -199,16 +199,60 @@
     <t>用例总个数</t>
   </si>
   <si>
-    <t>Test Case ID 测试用例编号</t>
-  </si>
-  <si>
-    <t>Test Item 测试项（即功能模块或函数）</t>
-  </si>
-  <si>
-    <t>Test Case Title 测试用例标题</t>
-  </si>
-  <si>
-    <t>Test Criticality重要级别</t>
+    <r>
+      <t xml:space="preserve">Test Case ID </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试用例编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Test Item </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试项（即功能模块或函数）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Test Case Title </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试用例标题</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Test Criticality</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>重要级别</t>
+    </r>
   </si>
   <si>
     <t>是否自动用例</t>
@@ -217,27 +261,114 @@
     <t>是否新增修改用例</t>
   </si>
   <si>
-    <t>Pre-condition 预置条件</t>
-  </si>
-  <si>
-    <t>Input 输入</t>
-  </si>
-  <si>
-    <t>Procedure 操作步骤</t>
-  </si>
-  <si>
-    <t>Output 预期结果</t>
-  </si>
-  <si>
-    <t>Result
-实际结果</t>
-  </si>
-  <si>
-    <t>Status
-是否通过</t>
-  </si>
-  <si>
-    <t>Remark 备注（在此描述使用的测试方法）</t>
+    <r>
+      <t xml:space="preserve">Pre-condition </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>预置条件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Input </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Procedure </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>操作步骤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Output </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>预期结果</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Result
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实际结果</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Status
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否通过</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Remark </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>备注</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color indexed="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（在此描述使用的测试方法）</t>
+    </r>
   </si>
   <si>
     <t>R01</t>
@@ -420,7 +551,57 @@
     <t>Emoji和多语言Unicode</t>
   </si>
   <si>
-    <t>介绍勾股定理 📐✖️➗ sqrt(a²+b²) 🎉 한글 Привет</t>
+    <r>
+      <t>介绍勾股定理 📐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>✖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>➗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> sqrt(a²+b²) 🎉 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="MS Gothic"/>
+        <charset val="134"/>
+      </rPr>
+      <t>한글</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Привет</t>
+    </r>
   </si>
   <si>
     <t>1.准备预置条件。
@@ -1336,7 +1517,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\.mm\.dd"/>
     <numFmt numFmtId="177" formatCode="yy\.mm\.dd"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="35">
     <font>
       <sz val="12"/>
       <name val="Arial"/>
@@ -1365,19 +1546,24 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="16"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF23724C"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1386,6 +1572,11 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF24496B"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1552,8 +1743,20 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="MS Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1574,19 +1777,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24496B"/>
+        <fgColor indexed="41"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F6FB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1599,18 +1796,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="41"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2087,28 +2272,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="16">
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
@@ -2117,122 +2293,131 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="19">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="20">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="19">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="19">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="21">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="20">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="22">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="19">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="23">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="21">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2255,146 +2440,137 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="centerContinuous"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="centerContinuous"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="10" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2448,6 +2624,12 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FFFFCC"/>
+      <color rgb="00CCFFFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2727,672 +2909,672 @@
   <sheetData>
     <row r="1" ht="9.9" customHeight="1"/>
     <row r="2" ht="23" customHeight="1" spans="2:12">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="3.9" customHeight="1"/>
     <row r="6" spans="2:12">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" ht="42" customHeight="1" spans="2:12">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="18" t="s">
+      <c r="F7" s="20"/>
+      <c r="G7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="20" t="s">
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
     </row>
     <row r="8" ht="42" customHeight="1" spans="2:12">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="18" t="s">
+      <c r="F8" s="20"/>
+      <c r="G8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="20" t="s">
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
     </row>
     <row r="9" ht="42" customHeight="1" spans="2:12">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20" t="s">
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="18" t="s">
+      <c r="F9" s="20"/>
+      <c r="G9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="20" t="s">
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
     </row>
     <row r="10" ht="42" customHeight="1" spans="2:12">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="20" t="s">
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="18" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="20" t="s">
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
     </row>
     <row r="11" ht="42" customHeight="1" spans="2:12">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20" t="s">
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="18" t="s">
+      <c r="F11" s="20"/>
+      <c r="G11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="20" t="s">
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
     </row>
     <row r="12" ht="3.9" customHeight="1" spans="2:12">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="22"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="21"/>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="23">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="22">
         <f>COUNTA('Test Cases测试用例'!A2:A46)</f>
         <v>45</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" ht="3.9" customHeight="1" spans="2:12">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
     </row>
     <row r="16" ht="72" customHeight="1" spans="2:12">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" ht="3.9" customHeight="1" spans="2:12">
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="2:12">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
     </row>
     <row r="19" ht="46.5" customHeight="1" spans="2:12">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="18" t="s">
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="19"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" ht="42" customHeight="1" spans="2:12">
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="20" t="s">
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="21"/>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" ht="42" customHeight="1" spans="2:12">
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="20" t="s">
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="L21" s="21"/>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="2:12">
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="21"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="20"/>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="21"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="20"/>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="29"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="21"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="21"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="20"/>
     </row>
     <row r="26" ht="3.9" customHeight="1" spans="2:12">
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="22"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="21"/>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" spans="2:12">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="18" t="s">
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="2:12">
-      <c r="B29" s="33">
+      <c r="B29" s="19">
         <v>1</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="27" t="s">
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
     </row>
     <row r="30" spans="2:12">
-      <c r="B30" s="33">
+      <c r="B30" s="19">
         <v>2</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="27" t="s">
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
     </row>
     <row r="31" spans="2:12">
-      <c r="B31" s="33">
+      <c r="B31" s="19">
         <v>3</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="27" t="s">
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
     </row>
     <row r="32" spans="2:12">
-      <c r="B32" s="33">
+      <c r="B32" s="19">
         <v>4</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="27" t="s">
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="34">
+      <c r="B33" s="32">
         <v>5</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="37" t="s">
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
     </row>
     <row r="34" spans="2:12">
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="22"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="21"/>
     </row>
     <row r="35" spans="2:12">
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
     </row>
     <row r="36" spans="2:12">
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="2:12">
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
     </row>
     <row r="38" spans="2:12">
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="43">
+      <c r="C38" s="41">
         <f>COUNTIF('Test Cases测试用例'!L2:L46,"OK")</f>
         <v>45</v>
       </c>
-      <c r="D38" s="40" t="s">
+      <c r="D38" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="42">
         <f>IF(E13=0,0,C38/E13)</f>
         <v>1</v>
       </c>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
     </row>
     <row r="39" spans="2:12">
-      <c r="B39" s="40" t="s">
+      <c r="B39" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="43">
+      <c r="C39" s="41">
         <f>COUNTIF('Test Cases测试用例'!L2:L46,"POK")</f>
         <v>0</v>
       </c>
-      <c r="D39" s="40" t="s">
+      <c r="D39" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="44">
+      <c r="E39" s="42">
         <f>IF(E13=0,0,C39/E13)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
     </row>
     <row r="40" spans="2:12">
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="43">
+      <c r="C40" s="41">
         <f>COUNTIF('Test Cases测试用例'!L2:L46,"NG")</f>
         <v>0</v>
       </c>
-      <c r="D40" s="40" t="s">
+      <c r="D40" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="44">
+      <c r="E40" s="42">
         <f>IF(E13=0,0,C40/E13)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
     </row>
     <row r="41" spans="2:12">
-      <c r="B41" s="45" t="s">
+      <c r="B41" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="46">
+      <c r="C41" s="44">
         <f>COUNTIF('Test Cases测试用例'!L2:L46,"NT")</f>
         <v>0</v>
       </c>
-      <c r="D41" s="45" t="s">
+      <c r="D41" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="47">
+      <c r="E41" s="45">
         <f>IF(E13=0,0,C41/E13)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
     </row>
     <row r="42" ht="3" customHeight="1" spans="2:12">
-      <c r="B42" s="48"/>
-      <c r="C42" s="49"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
     </row>
     <row r="43" spans="2:12">
-      <c r="B43" s="52" t="s">
+      <c r="B43" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="53">
+      <c r="C43" s="51">
         <f>E13</f>
         <v>45</v>
       </c>
-      <c r="D43" s="54"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="56">
@@ -3468,22 +3650,23 @@
   <dimension ref="A1:N46"/>
   <sheetFormatPr defaultColWidth="11.6307692307692" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="8" style="8" customWidth="1"/>
-    <col min="2" max="2" width="14" style="8" customWidth="1"/>
-    <col min="3" max="3" width="17" style="8" customWidth="1"/>
-    <col min="4" max="5" width="7" style="8" customWidth="1"/>
-    <col min="6" max="6" width="10" style="8" customWidth="1"/>
-    <col min="7" max="7" width="23" style="8" customWidth="1"/>
+    <col min="1" max="1" width="16.3307692307692" style="8" customWidth="1"/>
+    <col min="2" max="2" width="23.5461538461538" style="8" customWidth="1"/>
+    <col min="3" max="3" width="34.7923076923077" style="8" customWidth="1"/>
+    <col min="4" max="4" width="28.3923076923077" style="8" customWidth="1"/>
+    <col min="5" max="5" width="20" style="8" customWidth="1"/>
+    <col min="6" max="6" width="13.2538461538462" style="8" customWidth="1"/>
+    <col min="7" max="7" width="30.1692307692308" style="8" customWidth="1"/>
     <col min="8" max="8" width="29" style="8" customWidth="1"/>
-    <col min="9" max="9" width="34" style="8" customWidth="1"/>
+    <col min="9" max="9" width="31.9461538461538" style="8" customWidth="1"/>
     <col min="10" max="10" width="30" style="8" customWidth="1"/>
-    <col min="11" max="11" width="24" style="8" customWidth="1"/>
-    <col min="12" max="12" width="7" style="8" customWidth="1"/>
+    <col min="11" max="11" width="25.5615384615385" style="8" customWidth="1"/>
+    <col min="12" max="12" width="18.1" style="8" customWidth="1"/>
     <col min="13" max="13" width="32" style="8" customWidth="1"/>
     <col min="14" max="14" width="3.45384615384615" style="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1" spans="1:14">
+    <row r="1" ht="65" customHeight="1" spans="1:14">
       <c r="A1" s="10" t="s">
         <v>51</v>
       </c>
@@ -3496,10 +3679,10 @@
       <c r="D1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>56</v>
       </c>
       <c r="G1" s="10" t="s">
@@ -3523,46 +3706,46 @@
       <c r="M1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="11"/>
+      <c r="N1" s="12"/>
     </row>
     <row r="2" ht="132" customHeight="1" spans="1:14">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>76</v>
       </c>
       <c r="N2" s="9" t="s">
@@ -3570,43 +3753,43 @@
       </c>
     </row>
     <row r="3" ht="132" customHeight="1" spans="1:14">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="13" t="s">
         <v>84</v>
       </c>
       <c r="N3" s="9" t="s">
@@ -3614,43 +3797,43 @@
       </c>
     </row>
     <row r="4" ht="132" customHeight="1" spans="1:14">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="13" t="s">
         <v>92</v>
       </c>
       <c r="N4" s="9" t="s">
@@ -3658,43 +3841,43 @@
       </c>
     </row>
     <row r="5" ht="132" customHeight="1" spans="1:14">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="13" t="s">
         <v>100</v>
       </c>
       <c r="N5" s="9" t="s">
@@ -3702,1683 +3885,1683 @@
       </c>
     </row>
     <row r="6" ht="132" customHeight="1" spans="1:14">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="7" ht="132" customHeight="1" spans="1:14">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="13" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="8" ht="132" customHeight="1" spans="1:14">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="L8" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="13" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="9" ht="132" customHeight="1" spans="1:14">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="10" ht="132" customHeight="1" spans="1:14">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="13" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="11" ht="132" customHeight="1" spans="1:14">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="M11" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="12" ht="132" customHeight="1" spans="1:14">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="13" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="13" ht="132" customHeight="1" spans="1:14">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="13" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="14" ht="132" customHeight="1" spans="1:14">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="13" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="15" ht="132" customHeight="1" spans="1:14">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="L15" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="13" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="16" ht="132" customHeight="1" spans="1:14">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="13" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="17" ht="132" customHeight="1" spans="1:13">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="L17" s="15" t="s">
+      <c r="L17" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M17" s="14" t="s">
+      <c r="M17" s="13" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="18" ht="132" customHeight="1" spans="1:13">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="K18" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="L18" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="M18" s="13" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="19" ht="132" customHeight="1" spans="1:13">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="L19" s="15" t="s">
+      <c r="L19" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M19" s="14" t="s">
+      <c r="M19" s="13" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" ht="132" customHeight="1" spans="1:13">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="13" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="21" ht="132" customHeight="1" spans="1:13">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="K21" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="L21" s="15" t="s">
+      <c r="L21" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M21" s="14" t="s">
+      <c r="M21" s="13" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="22" ht="132" customHeight="1" spans="1:13">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="L22" s="13" t="s">
+      <c r="L22" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="13" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="23" ht="132" customHeight="1" spans="1:13">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="H23" s="14" t="s">
+      <c r="H23" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="J23" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="K23" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="L23" s="15" t="s">
+      <c r="L23" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M23" s="14" t="s">
+      <c r="M23" s="13" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="24" ht="132" customHeight="1" spans="1:13">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="K24" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="L24" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M24" s="12" t="s">
+      <c r="M24" s="13" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="25" ht="132" customHeight="1" spans="1:13">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="14" t="s">
+      <c r="H25" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="J25" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="K25" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="L25" s="15" t="s">
+      <c r="L25" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M25" s="14" t="s">
+      <c r="M25" s="13" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="26" ht="132" customHeight="1" spans="1:13">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="K26" s="12" t="s">
+      <c r="K26" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="L26" s="13" t="s">
+      <c r="L26" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M26" s="12" t="s">
+      <c r="M26" s="13" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="27" ht="132" customHeight="1" spans="1:13">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H27" s="14" t="s">
+      <c r="H27" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="I27" s="14" t="s">
+      <c r="I27" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="J27" s="14" t="s">
+      <c r="J27" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="K27" s="14" t="s">
+      <c r="K27" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="L27" s="15" t="s">
+      <c r="L27" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M27" s="14" t="s">
+      <c r="M27" s="13" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="28" ht="132" customHeight="1" spans="1:13">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="K28" s="12" t="s">
+      <c r="K28" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="L28" s="13" t="s">
+      <c r="L28" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M28" s="12" t="s">
+      <c r="M28" s="13" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="29" ht="132" customHeight="1" spans="1:13">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="J29" s="14" t="s">
+      <c r="J29" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="K29" s="14" t="s">
+      <c r="K29" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="L29" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M29" s="14" t="s">
+      <c r="M29" s="13" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="30" ht="132" customHeight="1" spans="1:13">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="K30" s="12" t="s">
+      <c r="K30" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="L30" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M30" s="12" t="s">
+      <c r="M30" s="13" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="31" ht="132" customHeight="1" spans="1:13">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="I31" s="14" t="s">
+      <c r="I31" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="J31" s="14" t="s">
+      <c r="J31" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="K31" s="14" t="s">
+      <c r="K31" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="L31" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M31" s="14" t="s">
+      <c r="M31" s="13" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="32" ht="132" customHeight="1" spans="1:13">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="K32" s="12" t="s">
+      <c r="K32" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="L32" s="13" t="s">
+      <c r="L32" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M32" s="12" t="s">
+      <c r="M32" s="13" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="33" ht="132" customHeight="1" spans="1:13">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="14" t="s">
+      <c r="G33" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="J33" s="14" t="s">
+      <c r="J33" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="K33" s="14" t="s">
+      <c r="K33" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M33" s="14" t="s">
+      <c r="M33" s="13" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="34" ht="132" customHeight="1" spans="1:13">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="I34" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="J34" s="12" t="s">
+      <c r="J34" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="K34" s="12" t="s">
+      <c r="K34" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="L34" s="13" t="s">
+      <c r="L34" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M34" s="12" t="s">
+      <c r="M34" s="13" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="35" ht="132" customHeight="1" spans="1:13">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="G35" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="H35" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="I35" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="J35" s="14" t="s">
+      <c r="J35" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="K35" s="14" t="s">
+      <c r="K35" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="L35" s="15" t="s">
+      <c r="L35" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M35" s="14" t="s">
+      <c r="M35" s="13" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="36" ht="132" customHeight="1" spans="1:13">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="K36" s="12" t="s">
+      <c r="K36" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="L36" s="13" t="s">
+      <c r="L36" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M36" s="12" t="s">
+      <c r="M36" s="13" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="37" ht="132" customHeight="1" spans="1:13">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G37" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H37" s="14" t="s">
+      <c r="H37" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="I37" s="14" t="s">
+      <c r="I37" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="J37" s="14" t="s">
+      <c r="J37" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="K37" s="14" t="s">
+      <c r="K37" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="L37" s="15" t="s">
+      <c r="L37" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M37" s="14" t="s">
+      <c r="M37" s="13" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="38" ht="132" customHeight="1" spans="1:13">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="G38" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="H38" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="I38" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J38" s="12" t="s">
+      <c r="J38" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K38" s="12" t="s">
+      <c r="K38" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L38" s="13" t="s">
+      <c r="L38" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M38" s="12" t="s">
+      <c r="M38" s="13" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="39" ht="132" customHeight="1" spans="1:13">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H39" s="14" t="s">
+      <c r="H39" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J39" s="14" t="s">
+      <c r="J39" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="K39" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L39" s="15" t="s">
+      <c r="L39" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M39" s="14" t="s">
+      <c r="M39" s="13" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="40" ht="132" customHeight="1" spans="1:13">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G40" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H40" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="I40" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J40" s="12" t="s">
+      <c r="J40" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K40" s="12" t="s">
+      <c r="K40" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L40" s="13" t="s">
+      <c r="L40" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M40" s="12" t="s">
+      <c r="M40" s="13" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="41" ht="132" customHeight="1" spans="1:13">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H41" s="14" t="s">
+      <c r="H41" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="I41" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J41" s="14" t="s">
+      <c r="J41" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K41" s="14" t="s">
+      <c r="K41" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L41" s="15" t="s">
+      <c r="L41" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M41" s="14" t="s">
+      <c r="M41" s="13" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="42" ht="132" customHeight="1" spans="1:13">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="I42" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J42" s="12" t="s">
+      <c r="J42" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K42" s="12" t="s">
+      <c r="K42" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L42" s="13" t="s">
+      <c r="L42" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M42" s="12" t="s">
+      <c r="M42" s="13" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="43" ht="132" customHeight="1" spans="1:13">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H43" s="14" t="s">
+      <c r="H43" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="I43" s="14" t="s">
+      <c r="I43" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J43" s="14" t="s">
+      <c r="J43" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="K43" s="14" t="s">
+      <c r="K43" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L43" s="15" t="s">
+      <c r="L43" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M43" s="14" t="s">
+      <c r="M43" s="13" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="44" ht="132" customHeight="1" spans="1:13">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H44" s="12" t="s">
+      <c r="H44" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="I44" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J44" s="12" t="s">
+      <c r="J44" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="K44" s="12" t="s">
+      <c r="K44" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L44" s="13" t="s">
+      <c r="L44" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M44" s="12" t="s">
+      <c r="M44" s="13" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="45" ht="132" customHeight="1" spans="1:13">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H45" s="14" t="s">
+      <c r="H45" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="I45" s="14" t="s">
+      <c r="I45" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J45" s="14" t="s">
+      <c r="J45" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="K45" s="14" t="s">
+      <c r="K45" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L45" s="15" t="s">
+      <c r="L45" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M45" s="14" t="s">
+      <c r="M45" s="13" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="46" ht="132" customHeight="1" spans="1:13">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="I46" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="L46" s="13" t="s">
+      <c r="L46" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M46" s="12" t="s">
+      <c r="M46" s="13" t="s">
         <v>369</v>
       </c>
     </row>
